--- a/플랜트구매품질팀_대시보드_Sample_r1.xlsx
+++ b/플랜트구매품질팀_대시보드_Sample_r1.xlsx
@@ -81419,5 +81419,7 @@
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{6a195c26-dcfe-42b9-b1d4-7b01330667c1}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/플랜트구매품질팀_대시보드_Sample_r1.xlsx
+++ b/플랜트구매품질팀_대시보드_Sample_r1.xlsx
@@ -81775,5 +81775,7 @@
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{47a9bdcd-7622-459d-a5c4-18061cb3ac1b}" removed="1"/>
+</clbl:labelList>
 </file>